--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
+        <v>91633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91641</v>
+        <v>91642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91642</v>
+        <v>91669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91674</v>
+        <v>91679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91679</v>
+        <v>91683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91683</v>
+        <v>91688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91690</v>
+        <v>91695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91695</v>
+        <v>91701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91701</v>
+        <v>91708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>130130916</v>
       </c>
       <c r="B3" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>130130916</v>
       </c>
       <c r="B3" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>130130916</v>
       </c>
       <c r="B3" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>130130916</v>
       </c>
       <c r="B3" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>130130916</v>
       </c>
       <c r="B3" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128637872</v>
       </c>
       <c r="B2" t="n">
-        <v>91708</v>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,133 +793,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>130130916</v>
-      </c>
-      <c r="B3" t="n">
-        <v>91778</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>vassara4, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>748806</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7456619</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>örtrikt dråg</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # grövre # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Mariana Jussila Wahlberg</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mariana Jussila Wahlberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39968-2025 artfynd.xlsx
+++ b/artfynd/A 39968-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,8 +798,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128637872</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>